--- a/factory/工厂配送麦安研+焙满香门店商品月度销售对比表_格式化模板.xlsx
+++ b/factory/工厂配送麦安研+焙满香门店商品月度销售对比表_格式化模板.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F6CE10-BCA9-46D3-97EA-F55CAB42EF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2AA128-074D-4FEA-AD38-D92FFBAFB661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="841" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="货品对比表6.1-6.30" sheetId="1" r:id="rId1"/>
-    <sheet name="货品销售排行表6.1-6.30" sheetId="4" r:id="rId2"/>
-    <sheet name="配送杏坛店产品销售排行表" sheetId="5" r:id="rId3"/>
+    <sheet name="商品对比表6.1-6.30" sheetId="1" r:id="rId1"/>
+    <sheet name="商品销售排行表6.1-6.30" sheetId="4" r:id="rId2"/>
+    <sheet name="配送杏坛店商品销售排行表" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -80,7 +80,7 @@
   </si>
   <si>
     <r>
-      <t>2026年6月1日至6月30日工厂配送麦安研门店+焙满香门店货品对比表及各类别产品销售排行</t>
+      <t>2026年6月1日至6月30日工厂配送麦安研门店+焙满香门店商品对比表及各类别产品销售排行</t>
     </r>
     <r>
       <rPr>
@@ -97,7 +97,7 @@
   </si>
   <si>
     <r>
-      <t>2026年6月1日至6月30日工厂配送麦安研+焙满香门店货品销售排行</t>
+      <t>2026年6月1日至6月30日工厂配送麦安研+焙满香门店商品销售排行</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>2026年6月1日至6月30日工厂配送麦安研杏坛门店货品销售排行表</t>
+    <t>2026年6月1日至6月30日工厂配送麦安研杏坛门店商品销售排行表</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
